--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD445EA-9268-4F7B-B345-BF583D628245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{069D28C0-2FDB-48AF-B8C4-5C7E3F352CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7661C27D-B2DB-4B55-9078-B340F773935F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10457159-6030-451C-934C-26CD8735A8A0}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AE8BD2-D5A8-4BA6-A11F-E5B05E178DAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72BF288-03FC-490B-9241-C7A47B4B1377}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{069D28C0-2FDB-48AF-B8C4-5C7E3F352CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{475EF220-137D-4CAA-857F-9B19A9947818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10457159-6030-451C-934C-26CD8735A8A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD938903-D544-4DB3-B6D6-DD2CFE0426D6}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72BF288-03FC-490B-9241-C7A47B4B1377}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B050F8D-246C-4D1D-B7F4-CC909892D789}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{475EF220-137D-4CAA-857F-9B19A9947818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B49C409-664D-4DD8-898B-612E07CF6104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD938903-D544-4DB3-B6D6-DD2CFE0426D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5008239-9B96-4B5B-A300-2680F4A6E759}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B050F8D-246C-4D1D-B7F4-CC909892D789}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F592590B-A3CA-4B67-BBB6-5E3D58C81BB3}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B49C409-664D-4DD8-898B-612E07CF6104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5230B58-A749-45CF-A3F9-B8B9C3ECE8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5008239-9B96-4B5B-A300-2680F4A6E759}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BF4B7F-B95C-44A7-A5A0-95AB86658260}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F592590B-A3CA-4B67-BBB6-5E3D58C81BB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29D5EF9-DC03-4207-9F7B-493DA2ADDEC5}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5230B58-A749-45CF-A3F9-B8B9C3ECE8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF0C005E-DE0D-46DC-9CDB-324BD0BA181B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BF4B7F-B95C-44A7-A5A0-95AB86658260}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{598E9540-3AD4-4BC6-8F8B-92831FB3CB5D}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29D5EF9-DC03-4207-9F7B-493DA2ADDEC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF8F162-CCC5-47E6-9923-A569AD7180C1}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF0C005E-DE0D-46DC-9CDB-324BD0BA181B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA81051B-A5A4-46C8-9149-287212585010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{598E9540-3AD4-4BC6-8F8B-92831FB3CB5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3446E2D8-BF4B-43C8-9353-762F495685AB}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF8F162-CCC5-47E6-9923-A569AD7180C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB2E0CC-2B64-48AC-B452-AC6DF137BE19}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA81051B-A5A4-46C8-9149-287212585010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BF87B6-559B-46D0-AB74-2E4B91D69C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3446E2D8-BF4B-43C8-9353-762F495685AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12360750-587C-41D8-88BA-F058BA85F411}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB2E0CC-2B64-48AC-B452-AC6DF137BE19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D14855-B2F9-4BEA-911F-B45821B94133}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BF87B6-559B-46D0-AB74-2E4B91D69C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FCA3676-02DC-489C-9463-3A281B100040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12360750-587C-41D8-88BA-F058BA85F411}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A13AE1C0-D3B9-43BC-9925-392676836597}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D14855-B2F9-4BEA-911F-B45821B94133}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0FC526-6A0C-4583-BF2A-E038378E036F}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_JPN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FCA3676-02DC-489C-9463-3A281B100040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81F4559F-52E5-4671-9B94-10CF2E691A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -5377,7 +5377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A13AE1C0-D3B9-43BC-9925-392676836597}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1111E61C-23DA-4FBE-92B8-4881E03BC272}">
   <dimension ref="B2:AF939"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -25062,7 +25062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0FC526-6A0C-4583-BF2A-E038378E036F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C18A5681-1C7D-4D77-B53D-7AE07ADA5D92}">
   <dimension ref="B9:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
